--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.84594573804605</v>
+        <v>7.124966182432483</v>
       </c>
       <c r="D2" t="n">
-        <v>43.71162858694792</v>
+        <v>7.103139645379037</v>
       </c>
       <c r="E2" t="n">
-        <v>8.199792414127536</v>
+        <v>1.332466267295725</v>
       </c>
       <c r="F2" t="n">
-        <v>8.152107581837452</v>
+        <v>1.324717482048586</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.44636090979098</v>
+        <v>4.460033647841033</v>
       </c>
       <c r="D3" t="n">
-        <v>27.40741342327301</v>
+        <v>4.453704681281865</v>
       </c>
       <c r="E3" t="n">
-        <v>8.199792414127536</v>
+        <v>1.332466267295725</v>
       </c>
       <c r="F3" t="n">
-        <v>8.152107581837452</v>
+        <v>1.324717482048586</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
